--- a/Hoadon/HD2026/HDRa/7/3502551856_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/7/3502551856_HDDienTuMayTinhTien.xlsx
@@ -2711,6 +2711,444 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>3501400999</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHÁCH SẠN DẦU KHÍ PTSC</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Số 09 - 11 Hoàng Diệu, Phường Vũng  Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>2.36E7</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>2.36E7</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>3502493964</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BOHO</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Số 66 Hạ Long, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>4475000.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>4475000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>4950000.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>4950000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>3502417787</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ PHONG VŨ VINSUN</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>I1 Thái Văn Lung, Khu Á Châu, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>1.724E7</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>1.724E7</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>3502417787</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ PHONG VŨ VINSUN</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>I1 Thái Văn Lung, Khu Á Châu, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>3090000.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>3090000.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>3502325007</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ CUNG ỨNG TÀU BIỂN VIỆT ÁNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Số 60/17 Phạm Hồng Thái, Phường Tam Thắng, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>3900000.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>3900000.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
